--- a/MainTop/19.12.2025 имена/19.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/19.12.2025 имена/19.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\19.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76D4921-362C-4046-8A95-C47E5AF9EB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88147508-5065-428D-9113-69A5F089AF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>штрихкод</t>
   </si>
   <si>
-    <t>количество</t>
-  </si>
-  <si>
     <t>Термобирки Максим</t>
   </si>
   <si>
@@ -419,6 +416,9 @@
   </si>
   <si>
     <t>OZN1325164077</t>
+  </si>
+  <si>
+    <t>Num_Copies</t>
   </si>
 </sst>
 </file>
@@ -835,15 +835,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -851,10 +851,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -862,10 +862,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -928,10 +928,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -950,10 +950,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -961,10 +961,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -972,10 +972,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -983,10 +983,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -1049,10 +1049,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -1060,10 +1060,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66">
         <v>1</v>
